--- a/tourist-calculations.xlsx
+++ b/tourist-calculations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9529fc23a191b0aa/Dokumente/Uni/HSLU/Master Thesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3714" documentId="8_{525B256F-E877-40D8-A7DE-2D739D04A2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D3C32FA-A00F-4D38-A4A3-FA695A788B4A}"/>
+  <xr:revisionPtr revIDLastSave="3813" documentId="8_{525B256F-E877-40D8-A7DE-2D739D04A2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECC640DD-8F38-45EA-A2E6-45D2E1D143C3}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="5" xr2:uid="{FB5E5E60-5ADE-4526-8864-4F9FF3FD4F19}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="14" activeTab="19" xr2:uid="{FB5E5E60-5ADE-4526-8864-4F9FF3FD4F19}"/>
   </bookViews>
   <sheets>
     <sheet name="hotel alldata" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,6 @@
     <sheet name="tourists private acco PT" sheetId="29" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="149">
   <si>
     <t>summer</t>
   </si>
@@ -495,6 +494,15 @@
   </si>
   <si>
     <t>arrival by public transportation rate</t>
+  </si>
+  <si>
+    <t>average number of short term camping spot tourists doing activities by PT</t>
+  </si>
+  <si>
+    <t>additional trips</t>
+  </si>
+  <si>
+    <t>total annual PT demand</t>
   </si>
 </sst>
 </file>
@@ -638,7 +646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -699,17 +707,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -738,20 +760,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1488,14 +1497,14 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F51C70-BDDC-476C-B2B3-C93856938E4D}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="41.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="44" bestFit="1" customWidth="1"/>
@@ -1787,7 +1796,7 @@
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="34">
+      <c r="A27" s="40">
         <v>45505</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -1814,7 +1823,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
+      <c r="A28" s="40"/>
       <c r="B28" s="5" t="s">
         <v>106</v>
       </c>
@@ -1839,7 +1848,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
+      <c r="A29" s="40"/>
       <c r="B29" s="5" t="s">
         <v>91</v>
       </c>
@@ -1864,7 +1873,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
+      <c r="A30" s="40"/>
       <c r="B30" s="5" t="s">
         <v>93</v>
       </c>
@@ -1917,12 +1926,18 @@
       <c r="D35" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+      <c r="E35" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="34">
+      <c r="A36" s="40">
         <v>45505</v>
       </c>
       <c r="B36" s="5" t="s">
@@ -1950,7 +1965,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="34"/>
+      <c r="A37" s="40"/>
       <c r="B37" s="5" t="s">
         <v>106</v>
       </c>
@@ -1976,7 +1991,7 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="34"/>
+      <c r="A38" s="40"/>
       <c r="B38" s="5" t="s">
         <v>91</v>
       </c>
@@ -2002,7 +2017,7 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="34"/>
+      <c r="A39" s="40"/>
       <c r="B39" s="5" t="s">
         <v>93</v>
       </c>
@@ -2026,6 +2041,35 @@
         <f t="shared" si="6"/>
         <v>19.088578121989503</v>
       </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="11">
+        <v>45323</v>
+      </c>
+      <c r="B42" s="8"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="11">
+        <v>45505</v>
+      </c>
+      <c r="B43" s="8">
+        <f>(12+15+14+21)*2+((8+10+9+14)*7)*2+(11+12+13+12+19)*5</f>
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="11">
+        <v>45597</v>
+      </c>
+      <c r="B44" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2156,11 +2200,11 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F13" s="3"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
     </row>
     <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="4"/>
@@ -2302,11 +2346,11 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F13" s="3"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
     </row>
     <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="4"/>
@@ -2445,7 +2489,7 @@
       <c r="B7" s="6">
         <v>0.745</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="30">
         <v>0.28570000000000001</v>
       </c>
       <c r="D7" s="4"/>
@@ -2479,7 +2523,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
+      <c r="A11" s="40">
         <v>45505</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -2510,7 +2554,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
+      <c r="A12" s="40"/>
       <c r="B12" s="5" t="s">
         <v>106</v>
       </c>
@@ -2539,7 +2583,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="5" t="s">
         <v>91</v>
       </c>
@@ -2572,7 +2616,7 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="34"/>
+      <c r="A14" s="40"/>
       <c r="B14" s="5" t="s">
         <v>93</v>
       </c>
@@ -2583,7 +2627,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2601,7 +2645,36 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E15" s="48"/>
+      <c r="E15" s="32"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="11">
+        <v>45323</v>
+      </c>
+      <c r="B17" s="8"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
+        <v>45505</v>
+      </c>
+      <c r="B18" s="8">
+        <f>(3+3+41+0)*2+((2+2+25+0)*7)*2+(1+1+1+18+0)*5</f>
+        <v>605</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
+        <v>45597</v>
+      </c>
+      <c r="B19" s="8"/>
     </row>
     <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="4"/>
@@ -3177,6 +3250,9 @@
       <c r="H8" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="I8" s="49" t="s">
+        <v>147</v>
+      </c>
       <c r="J8" s="9"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -3199,6 +3275,9 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
+      <c r="I9" s="5">
+        <v>20</v>
+      </c>
       <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -3221,6 +3300,9 @@
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
+      <c r="I10" s="5">
+        <v>16</v>
+      </c>
       <c r="J10" s="9"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -3242,6 +3324,9 @@
       <c r="H11" s="8">
         <f>($I4*$B$7*H$7)/4</f>
         <v>25.23072704258049</v>
+      </c>
+      <c r="I11" s="5">
+        <v>8</v>
       </c>
       <c r="J11" s="9"/>
     </row>
@@ -3257,8 +3342,12 @@
       <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="9"/>
+      <c r="A13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -3268,8 +3357,13 @@
       <c r="J13" s="9"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="9"/>
+      <c r="A14" s="11">
+        <v>45323</v>
+      </c>
+      <c r="B14" s="8">
+        <f>(440*2)*2+(94*4)*2+20*16</f>
+        <v>2832</v>
+      </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -3279,8 +3373,13 @@
       <c r="J14" s="9"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="9"/>
+      <c r="A15" s="11">
+        <v>45505</v>
+      </c>
+      <c r="B15" s="8">
+        <f>(61*7)*2+(107*4)*2+16*16</f>
+        <v>1966</v>
+      </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -3290,8 +3389,13 @@
       <c r="J15" s="9"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="9"/>
+      <c r="A16" s="11">
+        <v>45597</v>
+      </c>
+      <c r="B16" s="8">
+        <f>(11*4)*2+(25*4)*2+(8*16)</f>
+        <v>416</v>
+      </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -3779,7 +3883,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E023670-224E-4656-B623-8D01AB8D9359}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -3935,20 +4039,20 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="42"/>
+      <c r="A7" s="48"/>
       <c r="B7" s="12">
         <v>0.3</v>
       </c>
@@ -4053,20 +4157,20 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="42"/>
+      <c r="A13" s="48"/>
       <c r="B13" s="12">
         <v>0.5</v>
       </c>
@@ -4174,20 +4278,20 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="40"/>
+      <c r="A19" s="46"/>
       <c r="B19" s="12">
         <v>0.5</v>
       </c>
@@ -4208,18 +4312,18 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="40"/>
-      <c r="B20" s="36" t="s">
+      <c r="A20" s="46"/>
+      <c r="B20" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="44"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="41"/>
+      <c r="A21" s="47"/>
       <c r="B21" s="21">
         <v>0</v>
       </c>
@@ -4318,6 +4422,52 @@
       </c>
       <c r="G24" s="8">
         <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>45323</v>
+      </c>
+      <c r="B27" s="8">
+        <f>'hotel finalarea'!B38+'non-hotel finalarea'!B34+'campgrounds shortterm finalarea'!B42+'campgrounds longterm finalarea'!B17+'daytrip tourists finalarea'!B14+'tourists private acco PT'!D32</f>
+        <v>8378</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
+        <v>45505</v>
+      </c>
+      <c r="B28" s="8">
+        <f>'hotel finalarea'!B39+'non-hotel finalarea'!B35+'campgrounds shortterm finalarea'!B43+'campgrounds longterm finalarea'!B18+'daytrip tourists finalarea'!B15+'tourists private acco PT'!D33</f>
+        <v>9436</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
+        <v>45597</v>
+      </c>
+      <c r="B29" s="8">
+        <f>'hotel finalarea'!B40+'non-hotel finalarea'!B36+'campgrounds shortterm finalarea'!B44+'campgrounds longterm finalarea'!B19+'daytrip tourists finalarea'!B16+'tourists private acco PT'!D34</f>
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="5">
+        <f>B29*(30*3)+B28*(30*5+3)+B27*(30*4+2)</f>
+        <v>2600104</v>
       </c>
     </row>
   </sheetData>
@@ -4336,7 +4486,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6B22533-A62C-4274-8102-48E572B18B90}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -4378,7 +4528,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="33" t="s">
         <v>90</v>
       </c>
       <c r="B2" s="23">
@@ -4408,7 +4558,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
+      <c r="A3" s="33"/>
       <c r="B3" s="23">
         <v>45505</v>
       </c>
@@ -4436,7 +4586,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
+      <c r="A4" s="33"/>
       <c r="B4" s="23">
         <v>45597</v>
       </c>
@@ -4464,7 +4614,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="33" t="s">
         <v>91</v>
       </c>
       <c r="B5" s="23">
@@ -4494,7 +4644,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
+      <c r="A6" s="33"/>
       <c r="B6" s="23">
         <v>45505</v>
       </c>
@@ -4522,7 +4672,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
+      <c r="A7" s="33"/>
       <c r="B7" s="23">
         <v>45597</v>
       </c>
@@ -4550,7 +4700,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="33" t="s">
         <v>92</v>
       </c>
       <c r="B8" s="23">
@@ -4580,7 +4730,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
+      <c r="A9" s="33"/>
       <c r="B9" s="23">
         <v>45505</v>
       </c>
@@ -4608,7 +4758,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="23">
         <v>45597</v>
       </c>
@@ -4636,7 +4786,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="33" t="s">
         <v>93</v>
       </c>
       <c r="B11" s="23">
@@ -4666,7 +4816,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
+      <c r="A12" s="33"/>
       <c r="B12" s="23">
         <v>45505</v>
       </c>
@@ -4694,7 +4844,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="23">
         <v>45597</v>
       </c>
@@ -4814,7 +4964,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="33" t="s">
         <v>90</v>
       </c>
       <c r="B18" s="23">
@@ -4842,7 +4992,7 @@
       <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
+      <c r="A19" s="33"/>
       <c r="B19" s="23">
         <v>45505</v>
       </c>
@@ -4868,7 +5018,7 @@
       <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="23">
         <v>45597</v>
       </c>
@@ -4894,7 +5044,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="33" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="23">
@@ -4922,7 +5072,7 @@
       <c r="J21" s="8"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="23">
         <v>45505</v>
       </c>
@@ -4948,7 +5098,7 @@
       <c r="J22" s="8"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="23">
         <v>45597</v>
       </c>
@@ -4974,7 +5124,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="33" t="s">
         <v>92</v>
       </c>
       <c r="B24" s="23">
@@ -5002,7 +5152,7 @@
       <c r="J24" s="8"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="30"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="23">
         <v>45505</v>
       </c>
@@ -5028,7 +5178,7 @@
       <c r="J25" s="8"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="30"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="23">
         <v>45597</v>
       </c>
@@ -5054,7 +5204,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="33" t="s">
         <v>93</v>
       </c>
       <c r="B27" s="23">
@@ -5082,7 +5232,7 @@
       <c r="J27" s="8"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="23">
         <v>45505</v>
       </c>
@@ -5108,7 +5258,7 @@
       <c r="J28" s="8"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="30"/>
+      <c r="A29" s="33"/>
       <c r="B29" s="23">
         <v>45597</v>
       </c>
@@ -5131,6 +5281,41 @@
       <c r="J29" s="8">
         <f>((F13*2)*$J$16*$A$16)/2/5</f>
         <v>11.265099999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C32" s="11">
+        <v>45323</v>
+      </c>
+      <c r="D32" s="8">
+        <f>(79+37+23+303)*2+(4+2+1+15)*2+(121+48+24+406)*2+(10+4+2+35)*5*2</f>
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C33" s="11">
+        <v>45505</v>
+      </c>
+      <c r="D33" s="8">
+        <f>(71+33+42+336)*2+(4+2+2+14)*2+(10+4+4+30)*2*7+(14+5+5+42)*2*5</f>
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C34" s="11">
+        <v>45597</v>
+      </c>
+      <c r="D34" s="8">
+        <f>(5+9+2+87)*2+(1+1+1+4)*2+(1+1+1+6)*4*2+(1+2+1+11)*5*2</f>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -5293,7 +5478,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="33" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="23">
@@ -5323,7 +5508,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="23">
         <v>45505</v>
       </c>
@@ -5351,7 +5536,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
+      <c r="A9" s="33"/>
       <c r="B9" s="23">
         <v>45597</v>
       </c>
@@ -5379,7 +5564,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="33" t="s">
         <v>91</v>
       </c>
       <c r="B10" s="23">
@@ -5409,7 +5594,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
+      <c r="A11" s="33"/>
       <c r="B11" s="23">
         <v>45505</v>
       </c>
@@ -5437,7 +5622,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
+      <c r="A12" s="33"/>
       <c r="B12" s="23">
         <v>45597</v>
       </c>
@@ -5465,7 +5650,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="33" t="s">
         <v>92</v>
       </c>
       <c r="B13" s="23">
@@ -5495,7 +5680,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="23">
         <v>45505</v>
       </c>
@@ -5523,7 +5708,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="23">
         <v>45597</v>
       </c>
@@ -5551,7 +5736,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="33" t="s">
         <v>93</v>
       </c>
       <c r="B16" s="23">
@@ -5581,7 +5766,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="23">
         <v>45505</v>
       </c>
@@ -5609,7 +5794,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="23">
         <v>45597</v>
       </c>
@@ -5721,7 +5906,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="33" t="s">
         <v>90</v>
       </c>
       <c r="B23" s="23">
@@ -5748,7 +5933,7 @@
       <c r="J23" s="8"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="30"/>
+      <c r="A24" s="33"/>
       <c r="B24" s="23">
         <v>45505</v>
       </c>
@@ -5770,7 +5955,7 @@
       <c r="J24" s="8"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="30"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="23">
         <v>45597</v>
       </c>
@@ -5792,7 +5977,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="33" t="s">
         <v>91</v>
       </c>
       <c r="B26" s="23">
@@ -5816,7 +6001,7 @@
       <c r="J26" s="8"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
+      <c r="A27" s="33"/>
       <c r="B27" s="23">
         <v>45505</v>
       </c>
@@ -5838,7 +6023,7 @@
       <c r="J27" s="8"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="23">
         <v>45597</v>
       </c>
@@ -5860,7 +6045,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="33" t="s">
         <v>92</v>
       </c>
       <c r="B29" s="23">
@@ -5884,7 +6069,7 @@
       <c r="J29" s="8"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="30"/>
+      <c r="A30" s="33"/>
       <c r="B30" s="23">
         <v>45505</v>
       </c>
@@ -5906,7 +6091,7 @@
       <c r="J30" s="8"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="23">
         <v>45597</v>
       </c>
@@ -5928,7 +6113,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="33" t="s">
         <v>93</v>
       </c>
       <c r="B32" s="23">
@@ -5952,7 +6137,7 @@
       <c r="J32" s="8"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="30"/>
+      <c r="A33" s="33"/>
       <c r="B33" s="23">
         <v>45505</v>
       </c>
@@ -5974,7 +6159,7 @@
       <c r="J33" s="8"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="30"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="23">
         <v>45597</v>
       </c>
@@ -6007,27 +6192,27 @@
       <c r="A38" s="11">
         <v>45323</v>
       </c>
-      <c r="B38" s="5">
-        <f>(40+16+8+135)*2+(10+4+2+35)*5*2+(C32+C29+C26+C23)*2</f>
-        <v>1793.0413793103448</v>
+      <c r="B38" s="8">
+        <f>(40+16+8+135)*2+(10+4+2+35)*5*2+(79+37+23+303)*2</f>
+        <v>1792</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>45505</v>
       </c>
-      <c r="B39" s="5">
-        <f>(17+6+6+48)*4*2+(24+9+8+67)*5*2+(C33+C30+C27+C24)*2</f>
-        <v>2659.4451612903226</v>
+      <c r="B39" s="8">
+        <f>(17+6+6+48)*4*2+(24+9+8+67)*5*2+(71+33+42+336)*2</f>
+        <v>2660</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>45597</v>
       </c>
-      <c r="B40" s="5">
-        <f>(6+1+1+1)*4*2+(11+1+2+1)*5*2+(C34+C31+C28+C25)*2</f>
-        <v>427.48</v>
+      <c r="B40" s="8">
+        <f>(6+1+1+1)*4*2+(11+1+2+1)*5*2+(5+9+2+87)*2</f>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -6057,12 +6242,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
     </row>
     <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
@@ -6323,12 +6508,12 @@
       <c r="B15" s="15"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
     </row>
     <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
@@ -6586,12 +6771,12 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
     </row>
     <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
@@ -7276,7 +7461,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9FB17E-7898-48B6-BD0B-0B9F3CF87173}">
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -7579,7 +7764,7 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="35" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="23">
@@ -7615,7 +7800,7 @@
       <c r="L20" s="8"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="44"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="23">
         <v>45505</v>
       </c>
@@ -7649,7 +7834,7 @@
       <c r="L21" s="8"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="45"/>
+      <c r="A22" s="37"/>
       <c r="B22" s="23">
         <v>45597</v>
       </c>
@@ -7683,7 +7868,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="35" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="23">
@@ -7719,7 +7904,7 @@
       <c r="L23" s="8"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="44"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="23">
         <v>45505</v>
       </c>
@@ -7753,7 +7938,7 @@
       <c r="L24" s="8"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="45"/>
+      <c r="A25" s="37"/>
       <c r="B25" s="23">
         <v>45597</v>
       </c>
@@ -7787,7 +7972,7 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="35" t="s">
         <v>92</v>
       </c>
       <c r="B26" s="23">
@@ -7823,7 +8008,7 @@
       <c r="L26" s="8"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="44"/>
+      <c r="A27" s="36"/>
       <c r="B27" s="23">
         <v>45505</v>
       </c>
@@ -7857,7 +8042,7 @@
       <c r="L27" s="8"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="45"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="23">
         <v>45597</v>
       </c>
@@ -7891,7 +8076,7 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="35" t="s">
         <v>93</v>
       </c>
       <c r="B29" s="23">
@@ -7927,7 +8112,7 @@
       <c r="L29" s="8"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="44"/>
+      <c r="A30" s="36"/>
       <c r="B30" s="23">
         <v>45505</v>
       </c>
@@ -7961,7 +8146,7 @@
       <c r="L30" s="8"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="45"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="23">
         <v>45597</v>
       </c>
@@ -7994,17 +8179,46 @@
         <v>5.8083362911230791</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>45323</v>
+      </c>
+      <c r="B34" s="8">
+        <f>(1+1+1+4)*2+(62+25+12+209)*2+(5+2+2+15)*5*2+(23+11+3+87)*2</f>
+        <v>1118</v>
+      </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
+        <v>45505</v>
+      </c>
+      <c r="B35" s="8">
+        <f>(1+1+1+5)*2+(5+2+2+15)*4*2+(7+3+3+22)*5*2+(20+9+12+96)*2</f>
+        <v>832</v>
+      </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="11">
+        <v>45597</v>
+      </c>
+      <c r="B36" s="8">
+        <f>(1+1+1+1)*2+(1+1+1+3)*4*2+(1+1+1+6)*5*2+(1+3+1+25)*2</f>
+        <v>206</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8193,10 +8407,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="39" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="5">
@@ -8213,8 +8427,8 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="13">
         <f t="shared" ref="C13:D13" si="1">C12/$E$12</f>
         <v>0.71641791044776115</v>
@@ -8229,10 +8443,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="39" t="s">
         <v>0</v>
       </c>
       <c r="C14" s="5">
@@ -8249,8 +8463,8 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
       <c r="C15" s="13">
         <f t="shared" ref="C15:D15" si="3">C14/$E$14</f>
         <v>0.77309090909090905</v>
@@ -8265,10 +8479,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="5">
@@ -8285,8 +8499,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="32"/>
-      <c r="B17" s="32"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="13">
         <f t="shared" ref="C17:D17" si="4">C16/$E$16</f>
         <v>0.71370967741935487</v>
@@ -8301,10 +8515,10 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="39" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="5">
@@ -8321,8 +8535,8 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
-      <c r="B20" s="32"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="13">
         <f t="shared" ref="C20:D20" si="6">C19/$E$19</f>
         <v>0.71370967741935487</v>
@@ -8337,10 +8551,10 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="39" t="s">
         <v>0</v>
       </c>
       <c r="C21" s="5">
@@ -8357,8 +8571,8 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
-      <c r="B22" s="32"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="13">
         <f t="shared" ref="C22:D22" si="8">C21/$E$21</f>
         <v>0.76790123456790127</v>
@@ -8373,10 +8587,10 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="5">
@@ -8393,8 +8607,8 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
-      <c r="B24" s="32"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="13">
         <f t="shared" ref="C24:D24" si="9">C23/$E$23</f>
         <v>0.71370967741935487</v>
@@ -8409,10 +8623,10 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="39" t="s">
         <v>1</v>
       </c>
       <c r="C26" s="5">
@@ -8426,8 +8640,8 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
-      <c r="B27" s="32"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="13">
         <v>0</v>
       </c>
@@ -8439,10 +8653,10 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="39" t="s">
         <v>0</v>
       </c>
       <c r="C28" s="5">
@@ -8459,8 +8673,8 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="33"/>
-      <c r="B29" s="32"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="13">
         <f t="shared" ref="C29:D29" si="10">C28/$E$28</f>
         <v>0.80528511821974968</v>
@@ -8475,10 +8689,10 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="33" t="s">
+      <c r="A30" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C30" s="5">
@@ -8492,8 +8706,8 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
-      <c r="B31" s="32"/>
+      <c r="A31" s="38"/>
+      <c r="B31" s="39"/>
       <c r="C31" s="13">
         <v>0</v>
       </c>
@@ -8506,12 +8720,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B21:B22"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A16:A17"/>
@@ -8519,11 +8732,12 @@
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B26:B27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
